--- a/data/trans_camb/P1413-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1413-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,04</t>
+          <t>22,12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>15,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -6,36</t>
+          <t>-13,79; -6,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,95; -8,9</t>
+          <t>-16,06; -8,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 11,12</t>
+          <t>1,16; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,03</t>
+          <t>-5,95; 0,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -3,08</t>
+          <t>-10,45; -2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 25,6</t>
+          <t>18,61; 25,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -3,07</t>
+          <t>-8,41; -3,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; -6,6</t>
+          <t>-11,94; -6,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 18,83</t>
+          <t>12,63; 18,46</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,21; -26,53</t>
+          <t>-49,53; -27,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,17; -37,83</t>
+          <t>-58,23; -36,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 46,2</t>
+          <t>4,2; 41,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 3,61</t>
+          <t>-19,25; 3,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,33; -11,0</t>
+          <t>-34,31; -10,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,97; 92,73</t>
+          <t>58,78; 93,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -11,77</t>
+          <t>-28,79; -12,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,04; -24,39</t>
+          <t>-40,97; -24,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,33; 70,7</t>
+          <t>43,48; 69,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,97</t>
+          <t>12,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,48</t>
+          <t>8,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,46</t>
+          <t>-7,16; -3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -3,11</t>
+          <t>-6,9; -3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,86</t>
+          <t>2,7; 7,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,16</t>
+          <t>-2,56; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,03</t>
+          <t>-4,16; 0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 33,5</t>
+          <t>9,8; 14,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -1,43</t>
+          <t>-4,29; -1,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -2,17</t>
+          <t>-5,07; -2,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 21,9</t>
+          <t>6,84; 10,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>133,24%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,91; -31,23</t>
+          <t>-54,06; -29,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -29,19</t>
+          <t>-53,09; -27,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 53,23</t>
+          <t>20,43; 66,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 17,16</t>
+          <t>-17,51; 17,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 1,04</t>
+          <t>-28,6; 0,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,36; 269,57</t>
+          <t>64,55; 119,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -11,78</t>
+          <t>-32,11; -10,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,89; -18,02</t>
+          <t>-37,63; -17,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,78; 168,32</t>
+          <t>50,06; 86,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>6,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; -2,52</t>
+          <t>-10,19; -3,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; -1,2</t>
+          <t>-8,35; -1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 5,64</t>
+          <t>-2,27; 5,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,84</t>
+          <t>-3,25; 5,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 0,56</t>
+          <t>-6,8; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,95</t>
+          <t>7,6; 15,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,23</t>
+          <t>-5,41; 0,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -1,59</t>
+          <t>-6,2; -1,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,28</t>
+          <t>4,04; 9,2</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>107,33%</t>
+          <t>110,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,64; -25,22</t>
+          <t>-76,07; -32,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -9,55</t>
+          <t>-65,14; -12,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 63,47</t>
+          <t>-18,23; 61,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 57,16</t>
+          <t>-28,34; 59,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 7,39</t>
+          <t>-54,15; 5,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,33; 178,71</t>
+          <t>58,38; 184,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,99; 2,49</t>
+          <t>-44,89; 1,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,56; -15,72</t>
+          <t>-52,59; -13,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,5; 102,38</t>
+          <t>33,8; 102,32</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,51</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -5,55</t>
+          <t>-8,8; -5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -6,36</t>
+          <t>-9,58; -6,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,17</t>
+          <t>0,41; 4,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,9</t>
+          <t>-2,95; 0,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,53</t>
+          <t>-7,3; -3,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 25,9</t>
+          <t>9,39; 13,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -2,81</t>
+          <t>-5,16; -2,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -5,44</t>
+          <t>-7,91; -5,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,22</t>
+          <t>5,66; 8,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,5; -36,36</t>
+          <t>-51,8; -36,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,27; -41,8</t>
+          <t>-56,06; -41,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 20,12</t>
+          <t>2,36; 26,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 4,94</t>
+          <t>-14,42; 4,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,46; -19,39</t>
+          <t>-35,88; -19,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,81; 134,71</t>
+          <t>45,85; 72,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -16,45</t>
+          <t>-28,33; -16,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,37; -31,65</t>
+          <t>-43,09; -31,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,86; 89,53</t>
+          <t>30,43; 48,85</t>
         </is>
       </c>
     </row>
